--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -826,55 +826,58 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9314,0.0068,0.0197,0.0013</t>
-  </si>
-  <si>
-    <t>0.0080,0.0012,0.0001,0.9990</t>
-  </si>
-  <si>
-    <t>0.8373,0.0050,0.0015,0.0579</t>
-  </si>
-  <si>
-    <t>0.6678,0.0002,0.0010,0.3172</t>
-  </si>
-  <si>
-    <t>0.9923,0.0019,0.0017,0.0007</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9311,0.0068,0.0198,0.0013</t>
+  </si>
+  <si>
+    <t>0.0079,0.0012,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.8365,0.0050,0.0015,0.0583</t>
+  </si>
+  <si>
+    <t>0.6662,0.0002,0.0010,0.3199</t>
+  </si>
+  <si>
+    <t>0.9922,0.0019,0.0017,0.0007</t>
   </si>
   <si>
     <t>0.9865,0.0063,0.0020,0.0014</t>
   </si>
   <si>
-    <t>0.9865,0.0027,0.0043,0.0005</t>
+    <t>0.9865,0.0028,0.0043,0.0005</t>
   </si>
   <si>
     <t>0.9958,0.0011,0.0007,0.0001</t>
   </si>
   <si>
-    <t>0.9503,0.0645,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9869,0.0074,0.0012,0.0009</t>
+    <t>0.9498,0.0652,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9869,0.0075,0.0012,0.0009</t>
   </si>
   <si>
     <t>0.9929,0.0020,0.0013,0.0003</t>
   </si>
   <si>
-    <t>0.9937,0.0019,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.8623,0.0113,0.1273,0.0009</t>
-  </si>
-  <si>
-    <t>0.0276,0.0598,0.9501,0.0029</t>
-  </si>
-  <si>
-    <t>0.2302,0.0008,0.8709,0.0003</t>
-  </si>
-  <si>
-    <t>0.0300,0.0078,0.9791,0.0008</t>
-  </si>
-  <si>
-    <t>0.8301,0.0007,0.2315,0.0000</t>
+    <t>0.9936,0.0020,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.8618,0.0114,0.1277,0.0009</t>
+  </si>
+  <si>
+    <t>0.0274,0.0603,0.9501,0.0029</t>
+  </si>
+  <si>
+    <t>0.2292,0.0008,0.8714,0.0003</t>
+  </si>
+  <si>
+    <t>0.0298,0.0079,0.9792,0.0008</t>
+  </si>
+  <si>
+    <t>0.8295,0.0007,0.2322,0.0000</t>
   </si>
   <si>
     <t>0.0005,0.9992,0.0054,0.0001</t>
@@ -883,82 +886,82 @@
     <t>0.0012,0.9980,0.0011,0.0010</t>
   </si>
   <si>
-    <t>0.0079,0.9968,0.0040,0.0000</t>
+    <t>0.0079,0.9968,0.0041,0.0000</t>
   </si>
   <si>
     <t>0.0022,0.9960,0.0017,0.0022</t>
   </si>
   <si>
-    <t>0.0006,0.9990,0.0515,0.0000</t>
-  </si>
-  <si>
-    <t>0.3764,0.0020,0.7061,0.0027</t>
-  </si>
-  <si>
-    <t>0.1707,0.0086,0.8735,0.0052</t>
-  </si>
-  <si>
-    <t>0.0125,0.0001,0.9943,0.0001</t>
-  </si>
-  <si>
-    <t>0.0258,0.0019,0.9830,0.0007</t>
-  </si>
-  <si>
-    <t>0.0358,0.0011,0.9806,0.0006</t>
-  </si>
-  <si>
-    <t>0.0327,0.0003,0.9826,0.0004</t>
+    <t>0.0006,0.9990,0.0516,0.0000</t>
+  </si>
+  <si>
+    <t>0.3757,0.0020,0.7067,0.0027</t>
+  </si>
+  <si>
+    <t>0.1700,0.0087,0.8739,0.0052</t>
+  </si>
+  <si>
+    <t>0.0124,0.0001,0.9943,0.0001</t>
+  </si>
+  <si>
+    <t>0.0257,0.0019,0.9830,0.0007</t>
+  </si>
+  <si>
+    <t>0.0357,0.0011,0.9807,0.0006</t>
+  </si>
+  <si>
+    <t>0.0326,0.0003,0.9826,0.0004</t>
   </si>
   <si>
     <t>0.0196,0.0003,0.9839,0.0017</t>
   </si>
   <si>
-    <t>0.7714,0.2462,0.0195,0.0010</t>
-  </si>
-  <si>
-    <t>0.6613,0.4650,0.0263,0.0033</t>
-  </si>
-  <si>
-    <t>0.0019,0.0003,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0068,0.5180,0.9363,0.0011</t>
-  </si>
-  <si>
-    <t>0.9411,0.0007,0.0497,0.0002</t>
-  </si>
-  <si>
-    <t>0.8331,0.0125,0.1237,0.0006</t>
-  </si>
-  <si>
-    <t>0.1449,0.8797,0.0184,0.0017</t>
-  </si>
-  <si>
-    <t>0.0068,0.9756,0.5232,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.3154,0.9854,0.0002</t>
+    <t>0.7691,0.2489,0.0195,0.0010</t>
+  </si>
+  <si>
+    <t>0.6596,0.4673,0.0264,0.0033</t>
+  </si>
+  <si>
+    <t>0.0018,0.0003,0.9984,0.0001</t>
+  </si>
+  <si>
+    <t>0.0068,0.5211,0.9362,0.0011</t>
+  </si>
+  <si>
+    <t>0.9409,0.0007,0.0498,0.0002</t>
+  </si>
+  <si>
+    <t>0.8324,0.0126,0.1241,0.0006</t>
+  </si>
+  <si>
+    <t>0.1440,0.8804,0.0184,0.0017</t>
+  </si>
+  <si>
+    <t>0.0067,0.9757,0.5244,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.3168,0.9854,0.0002</t>
   </si>
   <si>
     <t>0.0029,0.0003,0.9938,0.0066</t>
   </si>
   <si>
-    <t>0.0487,0.0073,0.9574,0.0031</t>
-  </si>
-  <si>
-    <t>0.0146,0.0001,0.9656,0.0116</t>
-  </si>
-  <si>
-    <t>0.0011,0.4057,0.8965,0.0019</t>
+    <t>0.0486,0.0073,0.9575,0.0031</t>
+  </si>
+  <si>
+    <t>0.0145,0.0001,0.9657,0.0116</t>
+  </si>
+  <si>
+    <t>0.0011,0.4075,0.8964,0.0019</t>
   </si>
   <si>
     <t>0.0018,0.9885,0.0117,0.0075</t>
   </si>
   <si>
-    <t>0.0041,0.0202,0.9752,0.0030</t>
-  </si>
-  <si>
-    <t>0.0006,0.6292,0.0001,0.9912</t>
+    <t>0.0041,0.0202,0.9753,0.0030</t>
+  </si>
+  <si>
+    <t>0.0006,0.6309,0.0001,0.9912</t>
   </si>
   <si>
     <t>0.0002,0.9996,0.0036,0.0001</t>
@@ -970,37 +973,37 @@
     <t>0.0000,1.0000,0.0045,0.0001</t>
   </si>
   <si>
-    <t>0.0006,0.0130,0.9960,0.0008</t>
-  </si>
-  <si>
-    <t>0.0006,0.1012,0.9956,0.0002</t>
+    <t>0.0006,0.0131,0.9960,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.1017,0.9956,0.0002</t>
   </si>
   <si>
     <t>0.0138,0.0013,0.9852,0.0016</t>
   </si>
   <si>
-    <t>0.0237,0.0000,0.9922,0.0000</t>
+    <t>0.0236,0.0000,0.9922,0.0000</t>
   </si>
   <si>
     <t>0.0105,0.0007,0.9924,0.0003</t>
   </si>
   <si>
-    <t>0.0122,0.0066,0.9852,0.0014</t>
-  </si>
-  <si>
-    <t>0.9719,0.0140,0.0105,0.0002</t>
-  </si>
-  <si>
-    <t>0.9742,0.0014,0.0171,0.0003</t>
-  </si>
-  <si>
-    <t>0.9820,0.0062,0.0056,0.0016</t>
-  </si>
-  <si>
-    <t>0.3964,0.0012,0.6114,0.0007</t>
-  </si>
-  <si>
-    <t>0.9792,0.0009,0.0128,0.0003</t>
+    <t>0.0121,0.0066,0.9852,0.0014</t>
+  </si>
+  <si>
+    <t>0.9718,0.0141,0.0106,0.0002</t>
+  </si>
+  <si>
+    <t>0.9740,0.0015,0.0172,0.0003</t>
+  </si>
+  <si>
+    <t>0.9819,0.0063,0.0056,0.0017</t>
+  </si>
+  <si>
+    <t>0.3945,0.0013,0.6133,0.0007</t>
+  </si>
+  <si>
+    <t>0.9791,0.0009,0.0128,0.0003</t>
   </si>
   <si>
     <t>0.9861,0.0021,0.0051,0.0006</t>
@@ -1009,46 +1012,46 @@
     <t>0.9871,0.0007,0.0081,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9988,0.8151,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0741,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0065,0.0126,0.9897,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.9364,0.9286,0.0005</t>
+    <t>0.0001,0.9988,0.8152,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0745,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0065,0.0127,0.9897,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.9366,0.9288,0.0005</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9998,0.0003</t>
   </si>
   <si>
-    <t>0.0042,0.9962,0.0227,0.0001</t>
+    <t>0.0041,0.9962,0.0227,0.0001</t>
   </si>
   <si>
     <t>0.0006,0.9992,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.9873,0.0008,0.0113,0.0000</t>
-  </si>
-  <si>
-    <t>0.4057,0.0538,0.5406,0.0021</t>
-  </si>
-  <si>
-    <t>0.0153,0.0034,0.9887,0.0010</t>
-  </si>
-  <si>
-    <t>0.0009,0.9685,0.9571,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.9511,0.9707,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.5734,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9942,0.9411,0.0000</t>
+    <t>0.9873,0.0008,0.0114,0.0000</t>
+  </si>
+  <si>
+    <t>0.4037,0.0543,0.5420,0.0021</t>
+  </si>
+  <si>
+    <t>0.0153,0.0035,0.9887,0.0010</t>
+  </si>
+  <si>
+    <t>0.0009,0.9686,0.9572,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9513,0.9707,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.5735,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9942,0.9412,0.0000</t>
   </si>
   <si>
     <t>0.0047,0.0024,0.0006,0.9987</t>
@@ -1069,16 +1072,16 @@
     <t>0.0005,0.0007,0.0005,0.9999</t>
   </si>
   <si>
-    <t>0.0002,0.9942,0.9307,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9253,0.9474,0.0004</t>
-  </si>
-  <si>
-    <t>0.0019,0.9526,0.8773,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.9574,0.9584,0.0002</t>
+    <t>0.0002,0.9942,0.9308,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9256,0.9475,0.0004</t>
+  </si>
+  <si>
+    <t>0.0019,0.9530,0.8771,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.9577,0.9584,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.9986,0.9675,0.0000</t>
@@ -1087,49 +1090,49 @@
     <t>0.0002,0.9984,0.0975,0.0002</t>
   </si>
   <si>
-    <t>0.9939,0.0040,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9681,0.0217,0.0062,0.0018</t>
-  </si>
-  <si>
-    <t>0.9571,0.0620,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.9860,0.0120,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9794,0.0127,0.0037,0.0007</t>
-  </si>
-  <si>
-    <t>0.9880,0.0071,0.0015,0.0014</t>
-  </si>
-  <si>
-    <t>0.9594,0.0028,0.0197,0.0020</t>
-  </si>
-  <si>
-    <t>0.9530,0.0033,0.0056,0.0006</t>
+    <t>0.9939,0.0041,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9680,0.0218,0.0062,0.0018</t>
+  </si>
+  <si>
+    <t>0.9568,0.0625,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9859,0.0121,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9793,0.0128,0.0037,0.0007</t>
+  </si>
+  <si>
+    <t>0.9879,0.0071,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.9594,0.0028,0.0198,0.0020</t>
+  </si>
+  <si>
+    <t>0.9529,0.0033,0.0056,0.0006</t>
   </si>
   <si>
     <t>0.9883,0.0011,0.0028,0.0013</t>
   </si>
   <si>
-    <t>0.9901,0.0073,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9933,0.0014,0.0011,0.0005</t>
+    <t>0.9900,0.0074,0.0021,0.0006</t>
+  </si>
+  <si>
+    <t>0.9933,0.0015,0.0011,0.0005</t>
   </si>
   <si>
     <t>0.9938,0.0035,0.0015,0.0006</t>
   </si>
   <si>
-    <t>0.9827,0.0055,0.0035,0.0046</t>
+    <t>0.9827,0.0056,0.0036,0.0046</t>
   </si>
   <si>
     <t>0.9955,0.0063,0.0005,0.0001</t>
   </si>
   <si>
-    <t>0.9939,0.0024,0.0008,0.0006</t>
+    <t>0.9939,0.0025,0.0008,0.0006</t>
   </si>
   <si>
     <t>0.9884,0.0018,0.0029,0.0007</t>
@@ -1138,13 +1141,13 @@
     <t>0.0019,0.0001,0.9981,0.0002</t>
   </si>
   <si>
-    <t>0.0340,0.0014,0.9788,0.0009</t>
-  </si>
-  <si>
-    <t>0.9463,0.0012,0.0641,0.0001</t>
-  </si>
-  <si>
-    <t>0.0520,0.0017,0.9680,0.0008</t>
+    <t>0.0339,0.0014,0.9788,0.0009</t>
+  </si>
+  <si>
+    <t>0.9461,0.0012,0.0643,0.0001</t>
+  </si>
+  <si>
+    <t>0.0518,0.0017,0.9680,0.0008</t>
   </si>
   <si>
     <t>0.0001,0.9997,0.0003,0.0005</t>
@@ -1153,31 +1156,31 @@
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0942,0.9391,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.1108,0.9216,0.0206,0.0010</t>
+    <t>0.0936,0.9396,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.1099,0.9222,0.0206,0.0010</t>
   </si>
   <si>
     <t>0.0001,0.9997,0.0002,0.0004</t>
   </si>
   <si>
-    <t>0.7831,0.3364,0.0121,0.0004</t>
-  </si>
-  <si>
-    <t>0.3020,0.0432,0.6015,0.0078</t>
-  </si>
-  <si>
-    <t>0.0828,0.0083,0.9440,0.0019</t>
-  </si>
-  <si>
-    <t>0.4267,0.0201,0.5162,0.0037</t>
-  </si>
-  <si>
-    <t>0.2499,0.0168,0.8012,0.0062</t>
-  </si>
-  <si>
-    <t>0.0008,0.4017,0.4426,0.4588</t>
+    <t>0.7814,0.3386,0.0122,0.0004</t>
+  </si>
+  <si>
+    <t>0.3009,0.0436,0.6015,0.0079</t>
+  </si>
+  <si>
+    <t>0.0824,0.0084,0.9443,0.0019</t>
+  </si>
+  <si>
+    <t>0.4258,0.0202,0.5169,0.0037</t>
+  </si>
+  <si>
+    <t>0.2491,0.0169,0.8018,0.0062</t>
+  </si>
+  <si>
+    <t>0.0008,0.4029,0.4432,0.4575</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0024,0.0001</t>
@@ -1195,25 +1198,25 @@
     <t>0.0012,0.9972,0.0781,0.0003</t>
   </si>
   <si>
-    <t>0.4839,0.2946,0.1600,0.0025</t>
-  </si>
-  <si>
-    <t>0.1205,0.8487,0.0544,0.0137</t>
+    <t>0.4816,0.2967,0.1604,0.0025</t>
+  </si>
+  <si>
+    <t>0.1197,0.8496,0.0544,0.0137</t>
   </si>
   <si>
     <t>0.9970,0.0005,0.0009,0.0003</t>
   </si>
   <si>
-    <t>0.9843,0.0088,0.0017,0.0017</t>
-  </si>
-  <si>
-    <t>0.9908,0.0029,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9847,0.0018,0.0042,0.0012</t>
-  </si>
-  <si>
-    <t>0.9882,0.0171,0.0014,0.0003</t>
+    <t>0.9842,0.0089,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.9908,0.0029,0.0013,0.0013</t>
+  </si>
+  <si>
+    <t>0.9846,0.0018,0.0042,0.0012</t>
+  </si>
+  <si>
+    <t>0.9882,0.0172,0.0014,0.0003</t>
   </si>
   <si>
     <t>0.9926,0.0005,0.0034,0.0004</t>
@@ -1225,28 +1228,28 @@
     <t>0.9937,0.0003,0.0022,0.0002</t>
   </si>
   <si>
-    <t>0.0036,0.8382,0.9268,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.5790,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0518,0.9975,0.0004</t>
-  </si>
-  <si>
-    <t>0.0085,0.0350,0.9872,0.0005</t>
-  </si>
-  <si>
-    <t>0.9306,0.0030,0.0513,0.0003</t>
-  </si>
-  <si>
-    <t>0.3381,0.4728,0.0509,0.0078</t>
-  </si>
-  <si>
-    <t>0.1071,0.0005,0.9316,0.0031</t>
-  </si>
-  <si>
-    <t>0.7092,0.0212,0.2592,0.0048</t>
+    <t>0.0036,0.8390,0.9269,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.5811,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0521,0.9975,0.0004</t>
+  </si>
+  <si>
+    <t>0.0084,0.0352,0.9872,0.0005</t>
+  </si>
+  <si>
+    <t>0.9304,0.0030,0.0514,0.0003</t>
+  </si>
+  <si>
+    <t>0.3360,0.4758,0.0507,0.0078</t>
+  </si>
+  <si>
+    <t>0.1066,0.0005,0.9318,0.0031</t>
+  </si>
+  <si>
+    <t>0.7086,0.0213,0.2596,0.0048</t>
   </si>
   <si>
     <t>0.0084,0.0001,0.0010,0.9989</t>
@@ -1261,121 +1264,121 @@
     <t>0.0017,0.0002,0.0006,0.9998</t>
   </si>
   <si>
-    <t>0.0004,0.9822,0.9086,0.0002</t>
-  </si>
-  <si>
-    <t>0.9794,0.0007,0.0103,0.0003</t>
-  </si>
-  <si>
-    <t>0.0081,0.9856,0.0075,0.0093</t>
+    <t>0.0004,0.9822,0.9090,0.0002</t>
+  </si>
+  <si>
+    <t>0.9793,0.0007,0.0103,0.0003</t>
+  </si>
+  <si>
+    <t>0.0080,0.9857,0.0075,0.0093</t>
   </si>
   <si>
     <t>0.9902,0.0005,0.0033,0.0002</t>
   </si>
   <si>
-    <t>0.0353,0.9682,0.0111,0.0017</t>
-  </si>
-  <si>
-    <t>0.9911,0.0020,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.1210,0.0000,0.9360,0.0000</t>
-  </si>
-  <si>
-    <t>0.3999,0.0001,0.6639,0.0000</t>
+    <t>0.0350,0.9685,0.0111,0.0017</t>
+  </si>
+  <si>
+    <t>0.9910,0.0020,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.1204,0.0000,0.9363,0.0000</t>
+  </si>
+  <si>
+    <t>0.3994,0.0001,0.6643,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9643,0.0001,0.0268,0.0001</t>
-  </si>
-  <si>
-    <t>0.9906,0.0020,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.6755,0.0903,0.0650,0.0010</t>
-  </si>
-  <si>
-    <t>0.9770,0.0069,0.0060,0.0002</t>
-  </si>
-  <si>
-    <t>0.9257,0.0294,0.0203,0.0026</t>
-  </si>
-  <si>
-    <t>0.1288,0.7692,0.1279,0.0125</t>
-  </si>
-  <si>
-    <t>0.9307,0.0497,0.0218,0.0014</t>
-  </si>
-  <si>
-    <t>0.8659,0.0209,0.0920,0.0011</t>
-  </si>
-  <si>
-    <t>0.9925,0.0043,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9880,0.0106,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9783,0.0044,0.0047,0.0022</t>
+    <t>0.9642,0.0001,0.0269,0.0001</t>
+  </si>
+  <si>
+    <t>0.9906,0.0020,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.6743,0.0909,0.0650,0.0010</t>
+  </si>
+  <si>
+    <t>0.9769,0.0069,0.0060,0.0002</t>
+  </si>
+  <si>
+    <t>0.9254,0.0297,0.0203,0.0026</t>
+  </si>
+  <si>
+    <t>0.1278,0.7712,0.1280,0.0125</t>
+  </si>
+  <si>
+    <t>0.9304,0.0500,0.0219,0.0014</t>
+  </si>
+  <si>
+    <t>0.8654,0.0211,0.0923,0.0011</t>
+  </si>
+  <si>
+    <t>0.9925,0.0044,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.9879,0.0107,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9782,0.0045,0.0047,0.0023</t>
   </si>
   <si>
     <t>0.9906,0.0008,0.0031,0.0003</t>
   </si>
   <si>
-    <t>0.9936,0.0020,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9899,0.0050,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9843,0.0054,0.0029,0.0014</t>
+    <t>0.9935,0.0021,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9898,0.0050,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9842,0.0055,0.0029,0.0014</t>
   </si>
   <si>
     <t>0.9912,0.0012,0.0022,0.0003</t>
   </si>
   <si>
-    <t>0.6957,0.3919,0.0033,0.0020</t>
-  </si>
-  <si>
-    <t>0.1986,0.8220,0.0148,0.0038</t>
-  </si>
-  <si>
-    <t>0.6451,0.3849,0.0129,0.0022</t>
-  </si>
-  <si>
-    <t>0.9301,0.0027,0.0613,0.0001</t>
-  </si>
-  <si>
-    <t>0.9857,0.0089,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.9429,0.0208,0.0259,0.0004</t>
-  </si>
-  <si>
-    <t>0.9853,0.0028,0.0060,0.0002</t>
-  </si>
-  <si>
-    <t>0.9471,0.0429,0.0089,0.0030</t>
-  </si>
-  <si>
-    <t>0.0077,0.0078,0.9932,0.0003</t>
-  </si>
-  <si>
-    <t>0.8822,0.0379,0.0634,0.0009</t>
+    <t>0.6940,0.3941,0.0033,0.0020</t>
+  </si>
+  <si>
+    <t>0.1971,0.8232,0.0148,0.0038</t>
+  </si>
+  <si>
+    <t>0.6425,0.3879,0.0130,0.0022</t>
+  </si>
+  <si>
+    <t>0.9297,0.0027,0.0616,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0090,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.9426,0.0209,0.0260,0.0004</t>
+  </si>
+  <si>
+    <t>0.9853,0.0029,0.0061,0.0002</t>
+  </si>
+  <si>
+    <t>0.9469,0.0432,0.0089,0.0030</t>
+  </si>
+  <si>
+    <t>0.0077,0.0079,0.9932,0.0003</t>
+  </si>
+  <si>
+    <t>0.8816,0.0381,0.0637,0.0009</t>
   </si>
   <si>
     <t>0.0009,0.0001,0.9993,0.0000</t>
   </si>
   <si>
-    <t>0.0011,0.0195,0.9950,0.0006</t>
-  </si>
-  <si>
-    <t>0.0221,0.0023,0.9794,0.0027</t>
-  </si>
-  <si>
-    <t>0.0024,0.0843,0.9909,0.0002</t>
+    <t>0.0011,0.0197,0.9950,0.0006</t>
+  </si>
+  <si>
+    <t>0.0221,0.0024,0.9794,0.0027</t>
+  </si>
+  <si>
+    <t>0.0024,0.0848,0.9909,0.0002</t>
   </si>
   <si>
     <t>0.0022,0.0004,0.9982,0.0001</t>
@@ -1387,58 +1390,58 @@
     <t>0.0063,0.0003,0.9955,0.0002</t>
   </si>
   <si>
-    <t>0.0581,0.0035,0.9557,0.0020</t>
-  </si>
-  <si>
-    <t>0.0913,0.0018,0.9438,0.0015</t>
-  </si>
-  <si>
-    <t>0.4024,0.0424,0.5365,0.0059</t>
-  </si>
-  <si>
-    <t>0.0481,0.0231,0.9373,0.0049</t>
-  </si>
-  <si>
-    <t>0.0182,0.0399,0.9683,0.0007</t>
-  </si>
-  <si>
-    <t>0.0925,0.0036,0.9288,0.0038</t>
-  </si>
-  <si>
-    <t>0.1829,0.0167,0.8095,0.0088</t>
-  </si>
-  <si>
-    <t>0.1602,0.0280,0.8223,0.0031</t>
-  </si>
-  <si>
-    <t>0.3968,0.8032,0.0023,0.0002</t>
+    <t>0.0580,0.0035,0.9557,0.0020</t>
+  </si>
+  <si>
+    <t>0.0911,0.0018,0.9439,0.0015</t>
+  </si>
+  <si>
+    <t>0.4017,0.0426,0.5371,0.0059</t>
+  </si>
+  <si>
+    <t>0.0479,0.0233,0.9373,0.0049</t>
+  </si>
+  <si>
+    <t>0.0181,0.0404,0.9682,0.0007</t>
+  </si>
+  <si>
+    <t>0.0921,0.0036,0.9289,0.0038</t>
+  </si>
+  <si>
+    <t>0.1822,0.0168,0.8099,0.0088</t>
+  </si>
+  <si>
+    <t>0.1592,0.0282,0.8230,0.0031</t>
+  </si>
+  <si>
+    <t>0.3950,0.8043,0.0023,0.0002</t>
   </si>
   <si>
     <t>0.0036,0.9970,0.0027,0.0002</t>
   </si>
   <si>
-    <t>0.1188,0.9180,0.0082,0.0008</t>
-  </si>
-  <si>
-    <t>0.9368,0.0475,0.0118,0.0010</t>
-  </si>
-  <si>
-    <t>0.4134,0.6201,0.0155,0.0018</t>
-  </si>
-  <si>
-    <t>0.1613,0.8337,0.0186,0.0027</t>
-  </si>
-  <si>
-    <t>0.9770,0.0046,0.0063,0.0002</t>
-  </si>
-  <si>
-    <t>0.2917,0.0266,0.6967,0.0251</t>
-  </si>
-  <si>
-    <t>0.1473,0.0025,0.8814,0.0113</t>
-  </si>
-  <si>
-    <t>0.5359,0.0064,0.4763,0.0027</t>
+    <t>0.1175,0.9189,0.0082,0.0008</t>
+  </si>
+  <si>
+    <t>0.9364,0.0480,0.0118,0.0010</t>
+  </si>
+  <si>
+    <t>0.4105,0.6232,0.0155,0.0018</t>
+  </si>
+  <si>
+    <t>0.1599,0.8351,0.0185,0.0027</t>
+  </si>
+  <si>
+    <t>0.9769,0.0046,0.0063,0.0002</t>
+  </si>
+  <si>
+    <t>0.2910,0.0267,0.6973,0.0252</t>
+  </si>
+  <si>
+    <t>0.1466,0.0025,0.8819,0.0113</t>
+  </si>
+  <si>
+    <t>0.5348,0.0064,0.4772,0.0027</t>
   </si>
   <si>
     <t>0.0120,0.0008,0.9898,0.0011</t>
@@ -1447,7 +1450,7 @@
     <t>0.0072,0.0004,0.9929,0.0004</t>
   </si>
   <si>
-    <t>0.0166,0.0076,0.9785,0.0002</t>
+    <t>0.0165,0.0077,0.9786,0.0002</t>
   </si>
   <si>
     <t>0.0147,0.0019,0.9843,0.0022</t>
@@ -1456,25 +1459,25 @@
     <t>0.0087,0.0011,0.9919,0.0002</t>
   </si>
   <si>
-    <t>0.9849,0.0010,0.0052,0.0007</t>
-  </si>
-  <si>
-    <t>0.9602,0.0217,0.0083,0.0033</t>
-  </si>
-  <si>
-    <t>0.9236,0.0359,0.0031,0.0072</t>
-  </si>
-  <si>
-    <t>0.9769,0.0206,0.0022,0.0018</t>
-  </si>
-  <si>
-    <t>0.9367,0.0286,0.0165,0.0120</t>
-  </si>
-  <si>
-    <t>0.9525,0.0237,0.0039,0.0034</t>
-  </si>
-  <si>
-    <t>0.9856,0.0074,0.0020,0.0012</t>
+    <t>0.9848,0.0010,0.0052,0.0007</t>
+  </si>
+  <si>
+    <t>0.9600,0.0219,0.0083,0.0034</t>
+  </si>
+  <si>
+    <t>0.9229,0.0363,0.0031,0.0072</t>
+  </si>
+  <si>
+    <t>0.9767,0.0209,0.0022,0.0018</t>
+  </si>
+  <si>
+    <t>0.9362,0.0289,0.0166,0.0121</t>
+  </si>
+  <si>
+    <t>0.9522,0.0239,0.0039,0.0034</t>
+  </si>
+  <si>
+    <t>0.9856,0.0075,0.0020,0.0012</t>
   </si>
   <si>
     <t>0.9865,0.0009,0.0054,0.0004</t>
@@ -1483,10 +1486,10 @@
     <t>0.0111,0.0013,0.9916,0.0007</t>
   </si>
   <si>
-    <t>0.1034,0.0187,0.8935,0.0022</t>
-  </si>
-  <si>
-    <t>0.4358,0.0112,0.5024,0.0178</t>
+    <t>0.1033,0.0188,0.8934,0.0022</t>
+  </si>
+  <si>
+    <t>0.4346,0.0113,0.5034,0.0179</t>
   </si>
   <si>
     <t>0.0009,0.0002,0.9993,0.0000</t>
@@ -1495,55 +1498,55 @@
     <t>0.0006,0.0014,0.9988,0.0002</t>
   </si>
   <si>
-    <t>0.0059,0.0047,0.9933,0.0005</t>
+    <t>0.0059,0.0048,0.9933,0.0005</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0330,0.0102,0.9669,0.0016</t>
-  </si>
-  <si>
-    <t>0.0080,0.0029,0.9909,0.0009</t>
-  </si>
-  <si>
-    <t>0.0546,0.0357,0.9062,0.0058</t>
-  </si>
-  <si>
-    <t>0.7062,0.0045,0.2392,0.0052</t>
-  </si>
-  <si>
-    <t>0.6916,0.0011,0.2543,0.0036</t>
-  </si>
-  <si>
-    <t>0.9698,0.0147,0.0098,0.0002</t>
-  </si>
-  <si>
-    <t>0.9784,0.0112,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.9537,0.0673,0.0026,0.0011</t>
-  </si>
-  <si>
-    <t>0.9898,0.0057,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.8417,0.1390,0.0105,0.0027</t>
-  </si>
-  <si>
-    <t>0.9870,0.0029,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.9465,0.0518,0.0039,0.0011</t>
-  </si>
-  <si>
-    <t>0.9850,0.0061,0.0017,0.0014</t>
-  </si>
-  <si>
-    <t>0.9786,0.0032,0.0050,0.0035</t>
-  </si>
-  <si>
-    <t>0.0084,0.0685,0.9737,0.0011</t>
+    <t>0.0329,0.0103,0.9669,0.0016</t>
+  </si>
+  <si>
+    <t>0.0080,0.0029,0.9910,0.0009</t>
+  </si>
+  <si>
+    <t>0.0543,0.0359,0.9063,0.0058</t>
+  </si>
+  <si>
+    <t>0.7052,0.0045,0.2402,0.0052</t>
+  </si>
+  <si>
+    <t>0.6909,0.0011,0.2548,0.0036</t>
+  </si>
+  <si>
+    <t>0.9697,0.0148,0.0098,0.0002</t>
+  </si>
+  <si>
+    <t>0.9783,0.0113,0.0019,0.0012</t>
+  </si>
+  <si>
+    <t>0.9532,0.0681,0.0026,0.0011</t>
+  </si>
+  <si>
+    <t>0.9897,0.0057,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.8402,0.1404,0.0106,0.0027</t>
+  </si>
+  <si>
+    <t>0.9869,0.0030,0.0023,0.0008</t>
+  </si>
+  <si>
+    <t>0.9458,0.0525,0.0039,0.0011</t>
+  </si>
+  <si>
+    <t>0.9850,0.0062,0.0017,0.0014</t>
+  </si>
+  <si>
+    <t>0.9786,0.0033,0.0050,0.0036</t>
+  </si>
+  <si>
+    <t>0.0084,0.0690,0.9737,0.0011</t>
   </si>
   <si>
     <t>0.0036,0.0095,0.9954,0.0002</t>
@@ -1552,37 +1555,37 @@
     <t>0.0039,0.0021,0.9957,0.0002</t>
   </si>
   <si>
-    <t>0.0461,0.0190,0.9487,0.0022</t>
+    <t>0.0460,0.0191,0.9487,0.0022</t>
   </si>
   <si>
     <t>0.0094,0.0003,0.9948,0.0002</t>
   </si>
   <si>
-    <t>0.2181,0.0099,0.0780,0.2670</t>
-  </si>
-  <si>
-    <t>0.0656,0.0135,0.8901,0.0063</t>
+    <t>0.2173,0.0099,0.0781,0.2676</t>
+  </si>
+  <si>
+    <t>0.0654,0.0136,0.8902,0.0063</t>
   </si>
   <si>
     <t>0.0054,0.0002,0.9888,0.0166</t>
   </si>
   <si>
-    <t>0.8940,0.0001,0.0071,0.0206</t>
-  </si>
-  <si>
-    <t>0.0002,0.0081,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0170,0.0010,0.0017,0.9973</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0087,0.9999</t>
+    <t>0.8936,0.0001,0.0071,0.0208</t>
+  </si>
+  <si>
+    <t>0.0002,0.0082,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0169,0.0010,0.0017,0.9973</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.0088,0.9999</t>
   </si>
   <si>
     <t>0.0005,0.0004,0.0005,0.9999</t>
   </si>
   <si>
-    <t>0.4504,0.0135,0.0035,0.4245</t>
+    <t>0.4489,0.0136,0.0035,0.4268</t>
   </si>
 </sst>
 </file>
@@ -1968,7 +1971,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1982,7 +1985,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1996,7 +1999,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2010,7 +2013,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2024,7 +2027,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2038,7 +2041,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2052,7 +2055,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2066,7 +2069,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2080,7 +2083,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2094,7 +2097,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2108,7 +2111,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2122,7 +2125,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2136,7 +2139,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,7 +2153,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2164,7 +2167,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2178,7 +2181,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2192,7 +2195,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,7 +2209,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,7 +2223,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,7 +2237,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,7 +2251,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,7 +2265,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2276,7 +2279,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2290,7 +2293,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,7 +2307,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2318,7 +2321,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2332,7 +2335,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2346,7 +2349,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,7 +2363,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2374,7 +2377,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2388,7 +2391,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,7 +2405,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2416,7 +2419,7 @@
         <v>268</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2430,7 +2433,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2444,7 +2447,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,7 +2461,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2472,7 +2475,7 @@
         <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,7 +2489,7 @@
         <v>266</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,7 +2503,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,7 +2517,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2528,7 +2531,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,7 +2545,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,7 +2559,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,7 +2573,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2584,7 +2587,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,7 +2601,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,7 +2615,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,7 +2629,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,7 +2643,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,7 +2657,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,7 +2671,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2682,7 +2685,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,7 +2699,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,7 +2713,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2724,7 +2727,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2738,7 +2741,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2752,7 +2755,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2766,7 +2769,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2780,7 +2783,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2794,7 +2797,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2808,7 +2811,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,7 +2825,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,7 +2839,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,7 +2853,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,7 +2867,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,7 +2881,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,7 +2895,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,7 +2909,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2920,7 +2923,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,7 +2937,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2948,7 +2951,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,7 +2965,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,7 +2979,7 @@
         <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,7 +2993,7 @@
         <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,7 +3007,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3018,7 +3021,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3032,7 +3035,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3046,7 +3049,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3060,7 +3063,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3074,7 +3077,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3088,7 +3091,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,7 +3105,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,7 +3119,7 @@
         <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,7 +3133,7 @@
         <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,7 +3147,7 @@
         <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,7 +3161,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,7 +3175,7 @@
         <v>267</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3186,7 +3189,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3200,7 +3203,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3214,7 +3217,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3228,7 +3231,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3242,7 +3245,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3256,7 +3259,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3270,7 +3273,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3284,7 +3287,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3298,7 +3301,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3312,7 +3315,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3326,7 +3329,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3340,7 +3343,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3354,7 +3357,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3368,7 +3371,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3382,7 +3385,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3396,7 +3399,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,7 +3413,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,7 +3427,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3438,7 +3441,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3452,7 +3455,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,7 +3469,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,7 +3483,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,7 +3497,7 @@
         <v>267</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,7 +3511,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,7 +3525,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,7 +3539,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3550,7 +3553,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3564,7 +3567,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3578,7 +3581,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3592,7 +3595,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3606,7 +3609,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3617,10 +3620,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,7 +3637,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,7 +3651,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,7 +3665,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,7 +3679,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,7 +3693,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3701,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,7 +3721,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3732,7 +3735,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3746,7 +3749,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3760,7 +3763,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3774,7 +3777,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3788,7 +3791,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3802,7 +3805,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3816,7 +3819,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3830,7 +3833,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,7 +3847,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,7 +3861,7 @@
         <v>268</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,7 +3875,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,7 +3889,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3900,7 +3903,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3911,10 +3914,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3928,7 +3931,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3942,7 +3945,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3956,7 +3959,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3970,7 +3973,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3984,7 +3987,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3998,7 +4001,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,7 +4015,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4026,7 +4029,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4040,7 +4043,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4054,7 +4057,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4068,7 +4071,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4082,7 +4085,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4096,7 +4099,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,7 +4113,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,7 +4127,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4138,7 +4141,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4152,7 +4155,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4166,7 +4169,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4180,7 +4183,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4194,7 +4197,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,7 +4211,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4222,7 +4225,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4236,7 +4239,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4250,7 +4253,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4264,7 +4267,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4278,7 +4281,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4292,7 +4295,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4306,7 +4309,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4320,7 +4323,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4334,7 +4337,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4348,7 +4351,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,7 +4365,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4376,7 +4379,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4390,7 +4393,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4404,7 +4407,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4418,7 +4421,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4432,7 +4435,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4446,7 +4449,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4460,7 +4463,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4474,7 +4477,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4488,7 +4491,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,7 +4505,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,7 +4519,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,7 +4533,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,7 +4547,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,7 +4561,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,7 +4575,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,7 +4589,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4600,7 +4603,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4614,7 +4617,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4628,7 +4631,7 @@
         <v>266</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4642,7 +4645,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4656,7 +4659,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4670,7 +4673,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4684,7 +4687,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4698,7 +4701,7 @@
         <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,7 +4715,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,7 +4729,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4740,7 +4743,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4754,7 +4757,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4768,7 +4771,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4782,7 +4785,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4796,7 +4799,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4810,7 +4813,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4824,7 +4827,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4838,7 +4841,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,7 +4855,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,7 +4869,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4880,7 +4883,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,7 +4897,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,7 +4911,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4922,7 +4925,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4936,7 +4939,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4950,7 +4953,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4964,7 +4967,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4978,7 +4981,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4992,7 +4995,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5006,7 +5009,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5020,7 +5023,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,7 +5037,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5048,7 +5051,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5062,7 +5065,7 @@
         <v>266</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,7 +5079,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,7 +5093,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,7 +5107,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,7 +5121,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,7 +5135,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,7 +5149,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,7 +5163,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5174,7 +5177,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5188,7 +5191,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5202,7 +5205,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5216,7 +5219,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5230,7 +5233,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5244,7 +5247,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5258,7 +5261,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5272,7 +5275,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5286,7 +5289,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5300,7 +5303,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5314,7 +5317,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5328,7 +5331,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,7 +5345,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,7 +5359,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,7 +5373,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,7 +5387,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,7 +5401,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5409,10 +5412,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D248" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5426,7 +5429,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,7 +5443,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5454,7 +5457,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5468,7 +5471,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5482,7 +5485,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5496,7 +5499,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5510,7 +5513,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5521,10 +5524,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D256" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
